--- a/db.xlsx
+++ b/db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\doc-mailmerge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272C359F-D366-4BD8-8681-98011ED837E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D5CEE8-9D7D-4087-81A6-AD915774E30A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" tabRatio="796" firstSheet="1" activeTab="1" xr2:uid="{475FD880-DA8F-42E9-9BC5-8552D9C25862}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="429">
   <si>
     <t>Ведомость 
 ПНД-5</t>
@@ -1345,10 +1345,6 @@
   </si>
   <si>
     <t>Профильный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Русский язык
-</t>
   </si>
 </sst>
 </file>
@@ -17932,9 +17928,9 @@
       <c r="BI2" s="24"/>
       <c r="BJ2" s="24"/>
     </row>
-    <row r="3" spans="1:62" ht="24">
+    <row r="3" spans="1:62">
       <c r="A3" s="124" t="s">
-        <v>429</v>
+        <v>19</v>
       </c>
       <c r="B3" s="10">
         <v>78</v>
